--- a/Parametros_v86_programador.xlsx
+++ b/Parametros_v86_programador.xlsx
@@ -96,7 +96,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generado: 2026-07-04 · Fuente: Cotizador_Fiflouu__web__v86.html (motor por código, sin hoja de cálculo)</t>
+          <t xml:space="preserve">Generado: 2026-07-09 · Fuente: Cotizador_Fiflouu__web__v86.html (motor por código, sin hoja de cálculo)</t>
         </is>
       </c>
     </row>
